--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0001T0006Z000C1N57_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0001T0006Z000C1N57_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>28.95343906429341</v>
+        <v>4.704933847947679</v>
       </c>
       <c r="D2" t="n">
-        <v>29.08035929180815</v>
+        <v>4.725558384918824</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
